--- a/Cardiologie/Excel/cardio_9.xlsx
+++ b/Cardiologie/Excel/cardio_9.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Cardiologie\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19DE28A5-3FF2-4E92-8B2F-91F04DAA7C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8EB389D-DE87-4EF1-8648-30DB5437163B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="367">
   <si>
     <t>Un anévrisme est une dilatation localisée et temporaire d'un vaisseau artériel.</t>
   </si>
@@ -581,6 +581,546 @@
   </si>
   <si>
     <t>image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est une dilatation localisée et permanente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte définit l'anévrisme par ces deux critères </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'anévrisme vrai comprend toutes les tuniques de la paroi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'aorte est le premier siège de prédilection par ordre de fréquence </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'athérome est cité comme l'étiologie principale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le diamètre normal est d'environ 20 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le tabagisme est au contraire défini comme un facteur de risque majeur </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les antécédents familiaux d'AAA sont un facteur de risque associé </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La prédominance masculine est liée à la manifestation de la maladie athéroscléreuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La dilatation résulte de la disparition des fibres élastiques et de l'amincissement de la paroi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’anévrisme a effectivement tendance à augmenter de diamètre selon cette loi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le risque de rupture est réel et augmente avec le diamètre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le risque augmente nettement dès que le diamètre est ≥ 60 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La rupture provoque des douleurs intenses, un collapsus et parfois un choc </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La fissuration et la rupture se manifestent par des douleurs abdominales ou lombaires </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le bilan d’opérabilité inclut obligatoirement des épreuves respiratoires fonctionnelles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La fréquence de surveillance dépend du diamètre (ex: 1 à 3 ans pour 30-40 mm) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils sont traités par méthylprednisolone 16-32 mg/j puis doses dégressives </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La chirurgie est indiquée si le diamètre est ≥ 55 mm ou en cas d'échec médical </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte confirme le risque élevé de rupture pour ces formes rares </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils se manifestent par de la fièvre et des douleurs abdominales ou lombaires </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il est recommandé pour les fumeurs dès 65 ans et dès 50 ans si antécédents familiaux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils sont souvent découverts fortuitement par imagerie ou palpation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est une alternative qui n'a pas démontré de bénéfice de mortalité à long terme </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'endofuite est une complication spécifique à surveiller après ce traitement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle permet une évaluation du diamètre plus standardisée et non-opérateur dépendante </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un anévrisme douloureux constitue une indication opératoire d'urgence </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le bilan d'opérabilité chirurgicale comprend l'évaluation de ces deux fonctions </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'anévrisme inflammatoire est caractérisé par une fibrose périanévrismale importante </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils sont causés par contamination par voie hématogène ou par contiguïté </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La fibrose peut englober l'uretère et causer des coliques néphrétiques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement endoluminal impose une surveillance régulière par tomodensitométrie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le dépistage commence à 65 ans pour les fumeurs sans antécédents familiaux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leur contrôle strict est essentiel pour diminuer la morbidité et la mortalité </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le diagnostic peut souvent être posé par la palpation d'une masse pulsatile </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement devient chirurgical ou endovasculaire à partir de 55 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle englobe l'uretère et le sigmoïde, mais le texte cite la VCI et non la VCS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La fièvre et le syndrome inflammatoire biologique sont des signes cliniques courants </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'amaigrissement et l'anorexie sont des présentations cliniques citées </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces anévrismes nécessitent un traitement chirurgical ET antibiotique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il est recommandé de 50 à 75 ans en cas d'antécédents familiaux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une surveillance par échographie tous les 1 à 3 ans est nécessaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'information sur les conséquences doit impérativement précéder le dépistage </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles incluent l'infarctus, l'insuffisance rénale, respiratoire et cardiaque </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les tortuosités aortiques ou iliaques sont des limites anatomiques à cette technique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils sont au contraire plus fréquents chez les hommes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'athérome est l'étiologie principale des anévrismes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement chirurgical est nécessaire si le diamètre atteint 55 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les critères de dépistage mentionnés s'arrêtent effectivement à 75 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La gestion du risque de décès prématuré est un aspect de la prise en charge </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le diagnostic peut souvent être posé cliniquement par ce moyen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sa mortalité est de ~1,5 % contre ~4 % pour la chirurgie classique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le dépistage est suggéré pour les femmes de 50 à 75 ans avec antécédents </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le graphique montre une baisse de prévalence corrélée à la baisse du tabagisme </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement définitif des AAA ≥ 55mm est chirurgical ou interventionnel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'aorte abdominale sous-rénale est effectivement la localisation la plus fréquente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils entreprennent l'aorte sus-rénale, sous-rénale et/ou l'aorte thoracique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils sont au contraire cités comme étant le plus souvent asymptomatiques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'hématémèse est listée parmi les signes de fissuration et de rupture </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est listée comme un examen complémentaire pour cette localisation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indications de traitement (asymptomatique si &gt;55 ou 60mm) et techniques (Dacron ou endoprothèse) décrites </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mortalité Dacron ~ 10% vs endoprothèse ~ 2% </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risque de paraplégie mentionné pour l’aorte thoracique et non abdominale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Souvent situés sur les iliaques primitives, étiologie principale : athéromatose </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hommes &gt; 60 ans athéromateux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anévrismes bilatéraux dans 50 % des cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Association fréquente avec l’anévrisme de l’aorte abdominale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Présentation la plus fréquente : thrombose et embolisation périphérique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iatrogène : post-ponction artérielle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traitement médical (compression, thrombine) tenté avant la chirurgie si échec </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anévrismes des artères viscérales cités comme "(rares)" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'artère splénique est effectivement la localisation la plus fréquente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risque de rupture lors de la grossesse chez la femme jeune </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'embolisation est une technique, la chirurgie ou l'endovasculaire sont d'autres options </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indiqués pour les anévrismes symptomatiques ou asymptomatiques de l'artère hépatique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Souvent situés sur les iliaques primitives (et non externes) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risque de rupture dans la veine iliaque avec fistule artério-veineuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technique chirurgicale par greffe veineuse fémoro-poplitée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Définition : augmentation du diamètre &gt; 50% </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’anévrisme vrai comprend effectivement toutes les tuniques de la paroi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solution de continuité intima/média créant un hématome contenu par l’adventice (pas média) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viscéraux, rénaux et carotides cités comme localisations plus rares </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le diamètre normal est effectivement d’environ 20 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Défini lorsque le diamètre est ≥ 30 mm chez la femme </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le tabagisme est qualifié de facteur de risque majeur </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le graphique indique environ 1,7% pour les "Former Smokers" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le graphique montre un taux légèrement inférieur à 1% pour les "Never Smokers" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'évolution de la prévalence de l’AAA est parallèle à la diminution du tabagisme </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les prévalences pour "All" sont effectivement de 0,4% (femmes) et 1,7% (hommes) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prévalence plus élevée si AOMI, antécédents d’AIT/AVC ou insuffisance coronaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les phénomènes inflammatoires fragilisent la paroi qui s'amincit (pas s'épaissit) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte mentionne le rôle de facteurs génétiques (formes familiales) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anévrisme dans le cadre de maladies du tissu élastique (Marfan, Ehlers-Danlos) : rare </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La maladie de Behçet est citée comme étiologie d'anévrisme inflammatoire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'augmentation de taille est en moyenne de 2 à 5 mm/an </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'augmentation est au contraire de plus en plus rapide en fonction du diamètre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le risque augmente nettement lorsque le diamètre est ≥ 60 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’augmentation rapide du diamètre (&gt; 5 mm/6 mois) est un facteur de risque </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le risque est de 1% (hommes) à 4% (femmes) ; il devient majeur à 60 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Défini lorsque le diamètre est ≥ 35 mm chez l’homme </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signe de De Bakey = anévrisme sous-rénal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facteur de risque : augmentation rapide du diamètre (&gt; 5 mm/6 mois) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Masse pulsatile, expansive refoulant les mains à chaque systole </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un anévrisme douloureux doit faire poser l’indication opératoire d’urgence </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Découverte variable lors d'un bilan pour symptômes non spécifiques par scanner </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signe de De Bakey : main entre le pôle supérieur de l’anévrisme et le rebord costal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Douleurs abdominales ou lombaires aiguës caractéristiques de la fissuration </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La rupture intrapéritonéale cause un collapsus sévère brutal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rupture vers organe creux : duodénum, intestin grêle, côlon, veine cave inférieure </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La rupture intrapéritonéale cause un collapsus sévère brutal (rétropéritonéale : parfois transitoire) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La compression de la veine cave inférieure provoque un œdème des membres inférieurs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La migration d'emboles provoque des douleurs et un tableau d’ischémie d’un membre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migration d’emboles vers un ou plusieurs orteils (« orteils bleus ») </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’échographie abdominale est l'examen de premier choix </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Permet de visualiser les calcifications de la paroi vasculaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Examen simple, non invasif, de premier choix pour le dépistage et la surveillance </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Évaluation du diamètre maximal plus standardisée que par échographie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'Angioscanner (avec contraste) est indiqué uniquement pour guider la stratégie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les antiagrégants cités sont Aspirine, Clopidogrel, Ticlopidine (pas héparine) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mortalité postopératoire pour une chirurgie programmée : ~ 4 % </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La technique consiste en l'ouverture du sac anévrismal puis l'interposition d'une prothèse en Dacron </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document précise au contraire que les complications tardives (pseudo-anévrisme, infection) sont rares </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La technique classique consiste effectivement à suturer une prothèse en Dacron à l'intérieur du sac ouvert </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La nécrose colique est listée comme complication de la cure chirurgicale classique, pas endoluminale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte liste précisément ces complications pour la chirurgie programmée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'exclusion de l'anévrisme par l'endoprothèse provoque la thrombose complète du sac </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La mortalité du traitement endoluminal (~1,5%) est inférieure à celle de la chirurgie (~4%) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement endoluminal présente effectivement moins de complications cardiaques ou pulmonaires </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'endoprothèse exclut l'anévrisme de la circulation une fois ancrée aux collets </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils sont surveillés par échographie tous les 6 mois ; la chirurgie est pour les diamètres ≥ 55 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La surveillance post-endoprothèse se fait par tomodensitométrie avec contraste (recherche d'endofuite) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La technique endoluminale n’a pas démontré de bénéfice en termes de mortalité globale à long terme </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est le seuil d'indication opératoire (diamètre ≥ 55 mm ou croissance &gt; 5 mm en 6 mois) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'indication et la sélection des patients tiennent compte de ces deux facteurs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le bilan d'opérabilité inclut la recherche d'une coronaropathie (scintigraphie ou coronarographie) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une fonction hépatique très perturbée est associée à un risque hémorragique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'évaluation de la fonction rénale est un facteur pronostique important pour le bilan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le bilan d’opérabilité inclut effectivement un écho-Doppler des vaisseaux du cou </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'algorithme de prise en charge préconise une surveillance échographique tous les 6 mois </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'anévrisme asymptomatique est une indication opératoire dès que le diamètre est ≥ 55 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement de l'anévrisme rompu se fait le plus souvent par prothèse en Dacron </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La mortalité péri-opératoire de l'anévrisme rompu est de ~ 45 - 50 % </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un diagnostic précoce permet effectivement cette réduction de mortalité </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le dépistage est recommandé pour les femmes (et hommes) de 65 à 75 ans fumeuses ou anciennes fumeuses </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La surveillance est de tous les 6 à 12 mois pour un AAA entre 40 et 54 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils représentent effectivement 5 à 10 % de tous les anévrismes de l'aorte </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La surveillance pour cette taille (40-54 mm) est de tous les 6 à 12 mois (pas tous les mois) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La localisation la plus fréquente est au contraire l'aorte abdominale sous-rénale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La chirurgie est indiquée pour les formes inflammatoires si le diamètre est ≥ 55 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document préconise une surveillance tous les 1 à 3 ans pour un diamètre de 30 à 40 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les anévrismes infectieux sont dus à une contamination par voie hématogène ou par contiguïté </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le scanner montre une couronne inflammatoire hyperdense en dehors de la paroi calcifiée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les douleurs dorsales et interscapulaires sont des symptômes possibles (bien que rares) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La compression peut entraîner toux, dyspnée, bronchopneumonie et atélectasie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La rupture de l'aorte thoracique peut effectivement provoquer une hémoptysie ou un hémothorax </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La dysphagie est un signe de compression par un anévrisme thoracique, pas abdominal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'IRM et la Rx thorax (découverte fortuite) sont utilisées pour le diagnostic </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les anévrismes symptomatiques ou compliqués constituent une indication de traitement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les maladies du tissu élastique sont une cause citée de ces anévrismes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est le seuil d'indication pour un anévrisme asymptomatique de l'aorte ascendante </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un diamètre de 55 mm est le seuil d'indication opératoire pour l'aorte ascendante </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La mortalité de 2% correspond à l'endoprothèse (le Dacron est à ~ 10%) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un diamètre &gt; 60 mm est le seuil pour l'aorte descendante ou thoracoabdominale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette intervention complexe nécessite la réimplantation des troncs viscéraux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le risque de paraplégie est effectivement mentionné pour l'aorte thoracique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La rupture d'un anévrisme iliaque peut entraîner un hématome rétropéritonéal aigu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement chirurgical ou endovasculaire est indiqué si le diamètre est ≥ 4 cm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les anévrismes poplités représentent 70 % des anévrismes périphériques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'indication opératoire (Dacron ou endoprothèse) est posée si le diamètre est ≥ 4 cm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils sont au contraire bilatéraux dans 50 % des cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La présentation la plus fréquente est la thrombose et l'embolisation périphérique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces complications entraînent effectivement une ischémie aiguë </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement est indiqué pour les formes asymptomatiques si le diamètre est &gt; 2 cm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les anévrismes poplités sont traités par greffe veineuse fémoro-poplitée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le pontage (mise à plat et pontage) est le traitement des formes symptomatiques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce traitement (compression, thrombine) s'applique aux faux anévrismes fémoraux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils peuvent au contraire être observés sur le tronc cœliaque </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'HTA et l'hématurie sont des présentations cliniques possibles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La rupture peut entraîner un hémopéritoine aigu, une hémorragie digestive ou une hémobilie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est une indication de traitement pour prévenir le risque de rupture lors de la grossesse </t>
   </si>
 </sst>
 </file>
@@ -928,7 +1468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G181"/>
+  <dimension ref="A1:H181"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
@@ -937,7 +1477,7 @@
     <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>180</v>
       </c>
@@ -950,17 +1490,18 @@
       <c r="D1" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="2"/>
+      <c r="F1" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -970,8 +1511,14 @@
       <c r="C2" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -981,8 +1528,14 @@
       <c r="C3" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -992,8 +1545,14 @@
       <c r="C4" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>189</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1003,8 +1562,14 @@
       <c r="C5" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>190</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1014,8 +1579,14 @@
       <c r="C6" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>191</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1025,8 +1596,14 @@
       <c r="C7" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>192</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1036,8 +1613,14 @@
       <c r="C8" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>193</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1047,8 +1630,14 @@
       <c r="C9" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>194</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1058,8 +1647,14 @@
       <c r="C10" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>195</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1069,8 +1664,14 @@
       <c r="C11" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>196</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1080,8 +1681,14 @@
       <c r="C12" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>197</v>
+      </c>
+      <c r="E12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1091,8 +1698,14 @@
       <c r="C13" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>198</v>
+      </c>
+      <c r="E13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1102,8 +1715,14 @@
       <c r="C14" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>199</v>
+      </c>
+      <c r="E14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1113,8 +1732,14 @@
       <c r="C15" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>200</v>
+      </c>
+      <c r="E15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1124,8 +1749,14 @@
       <c r="C16" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1135,8 +1766,14 @@
       <c r="C17" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>202</v>
+      </c>
+      <c r="E17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1146,8 +1783,14 @@
       <c r="C18" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>203</v>
+      </c>
+      <c r="E18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1157,8 +1800,14 @@
       <c r="C19" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>204</v>
+      </c>
+      <c r="E19">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1168,8 +1817,14 @@
       <c r="C20" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
+        <v>205</v>
+      </c>
+      <c r="E20">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1179,8 +1834,14 @@
       <c r="C21" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>206</v>
+      </c>
+      <c r="E21">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1190,8 +1851,14 @@
       <c r="C22" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>207</v>
+      </c>
+      <c r="E22">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1201,8 +1868,14 @@
       <c r="C23" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>208</v>
+      </c>
+      <c r="E23">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1212,8 +1885,14 @@
       <c r="C24" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>209</v>
+      </c>
+      <c r="E24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1223,8 +1902,14 @@
       <c r="C25" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>210</v>
+      </c>
+      <c r="E25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1234,8 +1919,14 @@
       <c r="C26" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
+        <v>211</v>
+      </c>
+      <c r="E26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1245,8 +1936,14 @@
       <c r="C27" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>212</v>
+      </c>
+      <c r="E27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1256,8 +1953,14 @@
       <c r="C28" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>213</v>
+      </c>
+      <c r="E28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1267,8 +1970,14 @@
       <c r="C29" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
+        <v>214</v>
+      </c>
+      <c r="E29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1278,8 +1987,14 @@
       <c r="C30" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30" t="s">
+        <v>215</v>
+      </c>
+      <c r="E30">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1289,8 +2004,14 @@
       <c r="C31" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>216</v>
+      </c>
+      <c r="E31">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1300,8 +2021,14 @@
       <c r="C32" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>217</v>
+      </c>
+      <c r="E32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1311,8 +2038,14 @@
       <c r="C33" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>218</v>
+      </c>
+      <c r="E33">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1322,8 +2055,14 @@
       <c r="C34" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
+        <v>219</v>
+      </c>
+      <c r="E34">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1333,8 +2072,14 @@
       <c r="C35" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>220</v>
+      </c>
+      <c r="E35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -1344,8 +2089,14 @@
       <c r="C36" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36" t="s">
+        <v>221</v>
+      </c>
+      <c r="E36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1355,8 +2106,14 @@
       <c r="C37" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>222</v>
+      </c>
+      <c r="E37">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1366,8 +2123,14 @@
       <c r="C38" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>223</v>
+      </c>
+      <c r="E38">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1377,8 +2140,14 @@
       <c r="C39" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" t="s">
+        <v>224</v>
+      </c>
+      <c r="E39">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1388,8 +2157,14 @@
       <c r="C40" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
+        <v>225</v>
+      </c>
+      <c r="E40">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -1399,8 +2174,14 @@
       <c r="C41" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41" t="s">
+        <v>226</v>
+      </c>
+      <c r="E41">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -1410,8 +2191,14 @@
       <c r="C42" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" t="s">
+        <v>227</v>
+      </c>
+      <c r="E42">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -1421,8 +2208,14 @@
       <c r="C43" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43" t="s">
+        <v>228</v>
+      </c>
+      <c r="E43">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -1432,8 +2225,14 @@
       <c r="C44" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44" t="s">
+        <v>229</v>
+      </c>
+      <c r="E44">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -1443,8 +2242,14 @@
       <c r="C45" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45" t="s">
+        <v>230</v>
+      </c>
+      <c r="E45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -1454,8 +2259,14 @@
       <c r="C46" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D46" t="s">
+        <v>231</v>
+      </c>
+      <c r="E46">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -1465,8 +2276,14 @@
       <c r="C47" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47" t="s">
+        <v>232</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -1476,8 +2293,14 @@
       <c r="C48" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D48" t="s">
+        <v>233</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -1487,8 +2310,14 @@
       <c r="C49" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D49" t="s">
+        <v>234</v>
+      </c>
+      <c r="E49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -1498,8 +2327,14 @@
       <c r="C50" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D50" t="s">
+        <v>235</v>
+      </c>
+      <c r="E50">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -1509,8 +2344,14 @@
       <c r="C51" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D51" t="s">
+        <v>236</v>
+      </c>
+      <c r="E51">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -1520,8 +2361,14 @@
       <c r="C52" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D52" t="s">
+        <v>237</v>
+      </c>
+      <c r="E52">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -1531,8 +2378,14 @@
       <c r="C53" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D53" t="s">
+        <v>238</v>
+      </c>
+      <c r="E53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -1542,8 +2395,14 @@
       <c r="C54" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D54" t="s">
+        <v>239</v>
+      </c>
+      <c r="E54">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -1553,8 +2412,14 @@
       <c r="C55" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D55" t="s">
+        <v>240</v>
+      </c>
+      <c r="E55">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -1564,8 +2429,14 @@
       <c r="C56" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D56" t="s">
+        <v>241</v>
+      </c>
+      <c r="E56">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -1575,8 +2446,14 @@
       <c r="C57" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D57" t="s">
+        <v>242</v>
+      </c>
+      <c r="E57">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -1586,8 +2463,14 @@
       <c r="C58" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D58" t="s">
+        <v>243</v>
+      </c>
+      <c r="E58">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -1597,8 +2480,14 @@
       <c r="C59" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D59" t="s">
+        <v>244</v>
+      </c>
+      <c r="E59">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -1608,8 +2497,14 @@
       <c r="C60" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D60" t="s">
+        <v>245</v>
+      </c>
+      <c r="E60">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -1619,8 +2514,14 @@
       <c r="C61" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D61" t="s">
+        <v>246</v>
+      </c>
+      <c r="E61">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -1630,8 +2531,14 @@
       <c r="C62" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D62" t="s">
+        <v>247</v>
+      </c>
+      <c r="E62">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -1641,8 +2548,14 @@
       <c r="C63" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D63" t="s">
+        <v>248</v>
+      </c>
+      <c r="E63">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -1652,8 +2565,14 @@
       <c r="C64" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D64" t="s">
+        <v>249</v>
+      </c>
+      <c r="E64">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -1663,8 +2582,14 @@
       <c r="C65" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D65" t="s">
+        <v>250</v>
+      </c>
+      <c r="E65">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -1674,8 +2599,14 @@
       <c r="C66" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D66" t="s">
+        <v>251</v>
+      </c>
+      <c r="E66">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -1685,8 +2616,14 @@
       <c r="C67" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D67" t="s">
+        <v>252</v>
+      </c>
+      <c r="E67">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -1696,8 +2633,14 @@
       <c r="C68" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D68" t="s">
+        <v>253</v>
+      </c>
+      <c r="E68">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -1707,8 +2650,14 @@
       <c r="C69" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D69" t="s">
+        <v>254</v>
+      </c>
+      <c r="E69">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -1718,8 +2667,14 @@
       <c r="C70" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D70" t="s">
+        <v>255</v>
+      </c>
+      <c r="E70">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -1729,8 +2684,14 @@
       <c r="C71" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D71" t="s">
+        <v>256</v>
+      </c>
+      <c r="E71">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -1740,8 +2701,14 @@
       <c r="C72" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D72" t="s">
+        <v>257</v>
+      </c>
+      <c r="E72">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -1751,8 +2718,14 @@
       <c r="C73" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D73" t="s">
+        <v>258</v>
+      </c>
+      <c r="E73">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -1762,8 +2735,14 @@
       <c r="C74" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D74" t="s">
+        <v>259</v>
+      </c>
+      <c r="E74">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -1773,8 +2752,14 @@
       <c r="C75" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D75" t="s">
+        <v>260</v>
+      </c>
+      <c r="E75">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -1784,8 +2769,14 @@
       <c r="C76" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D76" t="s">
+        <v>261</v>
+      </c>
+      <c r="E76">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -1795,8 +2786,14 @@
       <c r="C77" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D77" t="s">
+        <v>262</v>
+      </c>
+      <c r="E77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -1806,8 +2803,14 @@
       <c r="C78" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D78" t="s">
+        <v>263</v>
+      </c>
+      <c r="E78">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -1817,8 +2820,14 @@
       <c r="C79" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D79" t="s">
+        <v>264</v>
+      </c>
+      <c r="E79">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -1828,8 +2837,14 @@
       <c r="C80" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D80" t="s">
+        <v>265</v>
+      </c>
+      <c r="E80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -1839,8 +2854,14 @@
       <c r="C81" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D81" t="s">
+        <v>266</v>
+      </c>
+      <c r="E81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -1850,8 +2871,14 @@
       <c r="C82" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D82" t="s">
+        <v>267</v>
+      </c>
+      <c r="E82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -1861,8 +2888,14 @@
       <c r="C83" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D83" t="s">
+        <v>268</v>
+      </c>
+      <c r="E83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -1872,8 +2905,14 @@
       <c r="C84" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D84" t="s">
+        <v>269</v>
+      </c>
+      <c r="E84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -1883,8 +2922,14 @@
       <c r="C85" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D85" t="s">
+        <v>270</v>
+      </c>
+      <c r="E85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -1894,8 +2939,14 @@
       <c r="C86" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D86" t="s">
+        <v>271</v>
+      </c>
+      <c r="E86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -1905,8 +2956,14 @@
       <c r="C87" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D87" t="s">
+        <v>272</v>
+      </c>
+      <c r="E87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -1916,8 +2973,14 @@
       <c r="C88" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D88" t="s">
+        <v>273</v>
+      </c>
+      <c r="E88">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -1927,8 +2990,14 @@
       <c r="C89" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D89" t="s">
+        <v>274</v>
+      </c>
+      <c r="E89">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -1938,8 +3007,14 @@
       <c r="C90" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D90" t="s">
+        <v>275</v>
+      </c>
+      <c r="E90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -1949,8 +3024,14 @@
       <c r="C91" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D91" t="s">
+        <v>276</v>
+      </c>
+      <c r="E91">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -1960,8 +3041,14 @@
       <c r="C92" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D92" t="s">
+        <v>277</v>
+      </c>
+      <c r="E92">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -1971,8 +3058,14 @@
       <c r="C93" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D93" t="s">
+        <v>278</v>
+      </c>
+      <c r="E93">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -1982,8 +3075,14 @@
       <c r="C94" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D94" t="s">
+        <v>279</v>
+      </c>
+      <c r="E94">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -1993,8 +3092,14 @@
       <c r="C95" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D95" t="s">
+        <v>280</v>
+      </c>
+      <c r="E95">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -2004,8 +3109,14 @@
       <c r="C96" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D96" t="s">
+        <v>281</v>
+      </c>
+      <c r="E96">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -2015,8 +3126,14 @@
       <c r="C97" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D97" t="s">
+        <v>282</v>
+      </c>
+      <c r="E97">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -2026,8 +3143,14 @@
       <c r="C98" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D98" t="s">
+        <v>283</v>
+      </c>
+      <c r="E98">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -2037,8 +3160,14 @@
       <c r="C99" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D99" t="s">
+        <v>284</v>
+      </c>
+      <c r="E99">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -2048,8 +3177,14 @@
       <c r="C100" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D100" t="s">
+        <v>285</v>
+      </c>
+      <c r="E100">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -2059,8 +3194,14 @@
       <c r="C101" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D101" t="s">
+        <v>286</v>
+      </c>
+      <c r="E101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -2070,8 +3211,14 @@
       <c r="C102" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D102" t="s">
+        <v>287</v>
+      </c>
+      <c r="E102">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -2081,8 +3228,14 @@
       <c r="C103" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D103" t="s">
+        <v>288</v>
+      </c>
+      <c r="E103">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -2092,8 +3245,14 @@
       <c r="C104" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D104" t="s">
+        <v>289</v>
+      </c>
+      <c r="E104">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -2103,8 +3262,14 @@
       <c r="C105" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D105" t="s">
+        <v>290</v>
+      </c>
+      <c r="E105">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -2114,8 +3279,14 @@
       <c r="C106" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D106" t="s">
+        <v>291</v>
+      </c>
+      <c r="E106">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>106</v>
       </c>
@@ -2125,8 +3296,14 @@
       <c r="C107" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D107" t="s">
+        <v>292</v>
+      </c>
+      <c r="E107">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -2136,8 +3313,14 @@
       <c r="C108" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D108" t="s">
+        <v>293</v>
+      </c>
+      <c r="E108">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>108</v>
       </c>
@@ -2147,8 +3330,14 @@
       <c r="C109" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D109" t="s">
+        <v>294</v>
+      </c>
+      <c r="E109">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -2158,8 +3347,14 @@
       <c r="C110" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D110" t="s">
+        <v>295</v>
+      </c>
+      <c r="E110">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>110</v>
       </c>
@@ -2169,8 +3364,14 @@
       <c r="C111" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D111" t="s">
+        <v>296</v>
+      </c>
+      <c r="E111">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>111</v>
       </c>
@@ -2180,8 +3381,14 @@
       <c r="C112" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D112" t="s">
+        <v>297</v>
+      </c>
+      <c r="E112">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>112</v>
       </c>
@@ -2191,8 +3398,14 @@
       <c r="C113" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D113" t="s">
+        <v>298</v>
+      </c>
+      <c r="E113">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>113</v>
       </c>
@@ -2202,8 +3415,14 @@
       <c r="C114" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D114" t="s">
+        <v>299</v>
+      </c>
+      <c r="E114">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>114</v>
       </c>
@@ -2213,8 +3432,14 @@
       <c r="C115" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D115" t="s">
+        <v>300</v>
+      </c>
+      <c r="E115">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>115</v>
       </c>
@@ -2224,8 +3449,14 @@
       <c r="C116" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D116" t="s">
+        <v>301</v>
+      </c>
+      <c r="E116">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>116</v>
       </c>
@@ -2235,8 +3466,14 @@
       <c r="C117" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D117" t="s">
+        <v>302</v>
+      </c>
+      <c r="E117">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -2246,8 +3483,14 @@
       <c r="C118" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D118" t="s">
+        <v>303</v>
+      </c>
+      <c r="E118">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>118</v>
       </c>
@@ -2257,8 +3500,14 @@
       <c r="C119" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D119" t="s">
+        <v>304</v>
+      </c>
+      <c r="E119">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>119</v>
       </c>
@@ -2268,8 +3517,14 @@
       <c r="C120" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D120" t="s">
+        <v>305</v>
+      </c>
+      <c r="E120">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>120</v>
       </c>
@@ -2279,8 +3534,14 @@
       <c r="C121" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D121" t="s">
+        <v>306</v>
+      </c>
+      <c r="E121">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>121</v>
       </c>
@@ -2290,8 +3551,14 @@
       <c r="C122" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D122" t="s">
+        <v>307</v>
+      </c>
+      <c r="E122">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>122</v>
       </c>
@@ -2301,8 +3568,14 @@
       <c r="C123" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D123" t="s">
+        <v>308</v>
+      </c>
+      <c r="E123">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>123</v>
       </c>
@@ -2312,8 +3585,14 @@
       <c r="C124" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D124" t="s">
+        <v>309</v>
+      </c>
+      <c r="E124">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>124</v>
       </c>
@@ -2323,8 +3602,14 @@
       <c r="C125" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D125" t="s">
+        <v>310</v>
+      </c>
+      <c r="E125">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>125</v>
       </c>
@@ -2334,8 +3619,14 @@
       <c r="C126" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D126" t="s">
+        <v>311</v>
+      </c>
+      <c r="E126">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>126</v>
       </c>
@@ -2345,8 +3636,14 @@
       <c r="C127" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D127" t="s">
+        <v>312</v>
+      </c>
+      <c r="E127">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>127</v>
       </c>
@@ -2356,8 +3653,14 @@
       <c r="C128" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D128" t="s">
+        <v>313</v>
+      </c>
+      <c r="E128">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>128</v>
       </c>
@@ -2367,8 +3670,14 @@
       <c r="C129" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D129" t="s">
+        <v>314</v>
+      </c>
+      <c r="E129">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>129</v>
       </c>
@@ -2378,8 +3687,14 @@
       <c r="C130" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D130" t="s">
+        <v>315</v>
+      </c>
+      <c r="E130">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>130</v>
       </c>
@@ -2389,8 +3704,14 @@
       <c r="C131" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D131" t="s">
+        <v>316</v>
+      </c>
+      <c r="E131">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>131</v>
       </c>
@@ -2400,8 +3721,14 @@
       <c r="C132" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D132" t="s">
+        <v>317</v>
+      </c>
+      <c r="E132">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>132</v>
       </c>
@@ -2411,8 +3738,14 @@
       <c r="C133" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D133" t="s">
+        <v>318</v>
+      </c>
+      <c r="E133">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>133</v>
       </c>
@@ -2422,8 +3755,14 @@
       <c r="C134" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D134" t="s">
+        <v>319</v>
+      </c>
+      <c r="E134">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>134</v>
       </c>
@@ -2433,8 +3772,14 @@
       <c r="C135" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D135" t="s">
+        <v>320</v>
+      </c>
+      <c r="E135">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>135</v>
       </c>
@@ -2444,8 +3789,14 @@
       <c r="C136" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D136" t="s">
+        <v>321</v>
+      </c>
+      <c r="E136">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>136</v>
       </c>
@@ -2455,8 +3806,14 @@
       <c r="C137" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D137" t="s">
+        <v>322</v>
+      </c>
+      <c r="E137">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>137</v>
       </c>
@@ -2466,8 +3823,14 @@
       <c r="C138" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D138" t="s">
+        <v>323</v>
+      </c>
+      <c r="E138">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>138</v>
       </c>
@@ -2477,8 +3840,14 @@
       <c r="C139" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D139" t="s">
+        <v>324</v>
+      </c>
+      <c r="E139">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>139</v>
       </c>
@@ -2488,8 +3857,14 @@
       <c r="C140" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D140" t="s">
+        <v>325</v>
+      </c>
+      <c r="E140">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>140</v>
       </c>
@@ -2499,8 +3874,14 @@
       <c r="C141" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D141" t="s">
+        <v>326</v>
+      </c>
+      <c r="E141">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>141</v>
       </c>
@@ -2510,8 +3891,14 @@
       <c r="C142" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D142" t="s">
+        <v>327</v>
+      </c>
+      <c r="E142">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>142</v>
       </c>
@@ -2521,8 +3908,14 @@
       <c r="C143" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D143" t="s">
+        <v>328</v>
+      </c>
+      <c r="E143">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>143</v>
       </c>
@@ -2532,8 +3925,14 @@
       <c r="C144" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D144" t="s">
+        <v>329</v>
+      </c>
+      <c r="E144">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>144</v>
       </c>
@@ -2543,8 +3942,14 @@
       <c r="C145" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D145" t="s">
+        <v>330</v>
+      </c>
+      <c r="E145">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>145</v>
       </c>
@@ -2554,8 +3959,14 @@
       <c r="C146" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D146" t="s">
+        <v>331</v>
+      </c>
+      <c r="E146">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>146</v>
       </c>
@@ -2565,8 +3976,14 @@
       <c r="C147" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D147" t="s">
+        <v>332</v>
+      </c>
+      <c r="E147">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>147</v>
       </c>
@@ -2576,8 +3993,14 @@
       <c r="C148" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D148" t="s">
+        <v>333</v>
+      </c>
+      <c r="E148">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>148</v>
       </c>
@@ -2587,8 +4010,14 @@
       <c r="C149" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D149" t="s">
+        <v>334</v>
+      </c>
+      <c r="E149">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>149</v>
       </c>
@@ -2598,8 +4027,14 @@
       <c r="C150" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D150" t="s">
+        <v>335</v>
+      </c>
+      <c r="E150">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>150</v>
       </c>
@@ -2609,8 +4044,14 @@
       <c r="C151" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D151" t="s">
+        <v>336</v>
+      </c>
+      <c r="E151">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>151</v>
       </c>
@@ -2620,8 +4061,14 @@
       <c r="C152" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D152" t="s">
+        <v>337</v>
+      </c>
+      <c r="E152">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>152</v>
       </c>
@@ -2631,8 +4078,14 @@
       <c r="C153" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D153" t="s">
+        <v>338</v>
+      </c>
+      <c r="E153">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>153</v>
       </c>
@@ -2642,16 +4095,31 @@
       <c r="C154" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D154" t="s">
+        <v>339</v>
+      </c>
+      <c r="E154">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>154</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C155" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="D155" t="s">
+        <v>340</v>
+      </c>
+      <c r="E155">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>155</v>
       </c>
@@ -2661,8 +4129,14 @@
       <c r="C156" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D156" t="s">
+        <v>341</v>
+      </c>
+      <c r="E156">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>156</v>
       </c>
@@ -2672,8 +4146,14 @@
       <c r="C157" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D157" t="s">
+        <v>342</v>
+      </c>
+      <c r="E157">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>157</v>
       </c>
@@ -2683,8 +4163,14 @@
       <c r="C158" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D158" t="s">
+        <v>343</v>
+      </c>
+      <c r="E158">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>158</v>
       </c>
@@ -2694,8 +4180,14 @@
       <c r="C159" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D159" t="s">
+        <v>344</v>
+      </c>
+      <c r="E159">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>159</v>
       </c>
@@ -2705,8 +4197,14 @@
       <c r="C160" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D160" t="s">
+        <v>345</v>
+      </c>
+      <c r="E160">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>160</v>
       </c>
@@ -2716,8 +4214,14 @@
       <c r="C161" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D161" t="s">
+        <v>346</v>
+      </c>
+      <c r="E161">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>161</v>
       </c>
@@ -2727,8 +4231,14 @@
       <c r="C162" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D162" t="s">
+        <v>347</v>
+      </c>
+      <c r="E162">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>162</v>
       </c>
@@ -2738,8 +4248,14 @@
       <c r="C163" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D163" t="s">
+        <v>348</v>
+      </c>
+      <c r="E163">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>163</v>
       </c>
@@ -2749,8 +4265,14 @@
       <c r="C164" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D164" t="s">
+        <v>349</v>
+      </c>
+      <c r="E164">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>164</v>
       </c>
@@ -2760,8 +4282,14 @@
       <c r="C165" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D165" t="s">
+        <v>350</v>
+      </c>
+      <c r="E165">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>165</v>
       </c>
@@ -2771,8 +4299,14 @@
       <c r="C166" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D166" t="s">
+        <v>351</v>
+      </c>
+      <c r="E166">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>166</v>
       </c>
@@ -2782,8 +4316,14 @@
       <c r="C167" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D167" t="s">
+        <v>352</v>
+      </c>
+      <c r="E167">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>167</v>
       </c>
@@ -2793,8 +4333,14 @@
       <c r="C168" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D168" t="s">
+        <v>353</v>
+      </c>
+      <c r="E168">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>168</v>
       </c>
@@ -2804,8 +4350,14 @@
       <c r="C169" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D169" t="s">
+        <v>354</v>
+      </c>
+      <c r="E169">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>169</v>
       </c>
@@ -2815,8 +4367,14 @@
       <c r="C170" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D170" t="s">
+        <v>355</v>
+      </c>
+      <c r="E170">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>170</v>
       </c>
@@ -2826,8 +4384,14 @@
       <c r="C171" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D171" t="s">
+        <v>356</v>
+      </c>
+      <c r="E171">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>171</v>
       </c>
@@ -2837,8 +4401,14 @@
       <c r="C172" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D172" t="s">
+        <v>357</v>
+      </c>
+      <c r="E172">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>172</v>
       </c>
@@ -2848,8 +4418,14 @@
       <c r="C173" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D173" t="s">
+        <v>358</v>
+      </c>
+      <c r="E173">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>173</v>
       </c>
@@ -2859,8 +4435,14 @@
       <c r="C174" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D174" t="s">
+        <v>359</v>
+      </c>
+      <c r="E174">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>174</v>
       </c>
@@ -2870,8 +4452,14 @@
       <c r="C175" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D175" t="s">
+        <v>360</v>
+      </c>
+      <c r="E175">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>175</v>
       </c>
@@ -2881,8 +4469,14 @@
       <c r="C176" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D176" t="s">
+        <v>361</v>
+      </c>
+      <c r="E176">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>176</v>
       </c>
@@ -2892,8 +4486,14 @@
       <c r="C177" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D177" t="s">
+        <v>362</v>
+      </c>
+      <c r="E177">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>177</v>
       </c>
@@ -2903,8 +4503,14 @@
       <c r="C178" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D178" t="s">
+        <v>363</v>
+      </c>
+      <c r="E178">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>178</v>
       </c>
@@ -2914,8 +4520,14 @@
       <c r="C179" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D179" t="s">
+        <v>364</v>
+      </c>
+      <c r="E179">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>179</v>
       </c>
@@ -2925,8 +4537,14 @@
       <c r="C180" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D180" t="s">
+        <v>365</v>
+      </c>
+      <c r="E180">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>180</v>
       </c>
@@ -2935,6 +4553,12 @@
       </c>
       <c r="C181" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="D181" t="s">
+        <v>366</v>
+      </c>
+      <c r="E181">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Cardiologie/Excel/cardio_9.xlsx
+++ b/Cardiologie/Excel/cardio_9.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Cardiologie\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8EB389D-DE87-4EF1-8648-30DB5437163B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014CE1A2-4AD6-4449-A059-45B059BD69E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="368">
   <si>
     <t>Un anévrisme est une dilatation localisée et temporaire d'un vaisseau artériel.</t>
   </si>
@@ -1121,6 +1121,9 @@
   </si>
   <si>
     <t xml:space="preserve">C'est une indication de traitement pour prévenir le risque de rupture lors de la grossesse </t>
+  </si>
+  <si>
+    <t>Page</t>
   </si>
 </sst>
 </file>
@@ -1490,7 +1493,9 @@
       <c r="D1" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="E1" s="2"/>
+      <c r="E1" s="2" t="s">
+        <v>367</v>
+      </c>
       <c r="F1" s="2" t="s">
         <v>184</v>
       </c>
